--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487081_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487081_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1186</v>
+        <v>5.1037</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9406</v>
+        <v>2.8186</v>
       </c>
       <c r="F2" t="n">
-        <v>2.178</v>
+        <v>2.2851</v>
       </c>
       <c r="G2" t="n">
         <v>2.4636</v>
@@ -610,13 +610,13 @@
         <v>2.3161</v>
       </c>
       <c r="S2" t="n">
-        <v>1.392</v>
+        <v>1.3772</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5315</v>
+        <v>0.4095</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8606</v>
+        <v>0.9677</v>
       </c>
       <c r="V2" t="n">
         <v>1.842</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2909</v>
+        <v>2.75</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4149</v>
+        <v>-0.0362</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7058</v>
+        <v>2.7861</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9616</v>
@@ -688,13 +688,13 @@
         <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5731000000000001</v>
+        <v>1.0321</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2406</v>
+        <v>0.1382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8136</v>
+        <v>0.8939</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4087</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9502</v>
+        <v>2.225</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7322</v>
+        <v>-0.6268</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6824</v>
+        <v>2.8518</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0471</v>
+        <v>1.3081</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3892</v>
+        <v>0.3084</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4363</v>
+        <v>0.9996</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4676</v>
+        <v>1.3945</v>
       </c>
       <c r="K4" t="n">
-        <v>0.419</v>
+        <v>0.7761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0486</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4205</v>
+        <v>-0.0864</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8082</v>
+        <v>-0.4677</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3877</v>
+        <v>0.3813</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>2.7021</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8435</v>
+        <v>0.661</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6954</v>
+        <v>0.3021</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1482</v>
+        <v>0.3589</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4106</v>
+        <v>0.4489</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4106</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>P. ALBISU ASTIGARRAGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7332</v>
+        <v>1.382</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0651</v>
+        <v>-0.321</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7983</v>
+        <v>1.703</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3081</v>
+        <v>1.5952</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3084</v>
+        <v>1.0661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9996</v>
+        <v>0.5291</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3945</v>
+        <v>1.8087</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7761</v>
+        <v>1.8008</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0864</v>
+        <v>-0.2135</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4677</v>
+        <v>-0.7347</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3813</v>
+        <v>0.5212</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.193</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8951</v>
+        <v>-4.8252</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7021</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1692</v>
+        <v>0.9505</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1361</v>
+        <v>-0.0462</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3053</v>
+        <v>0.9967</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4489</v>
+        <v>1.9245</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5717</v>
+        <v>2.7418</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1228</v>
+        <v>-0.8173</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2945</v>
+        <v>1.3272</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4033</v>
+        <v>1.4628</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1088</v>
+        <v>-0.1356</v>
       </c>
       <c r="G6" t="n">
         <v>-0.227</v>
@@ -922,13 +922,13 @@
         <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.433</v>
+        <v>-0.4002</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.238</v>
+        <v>-0.1785</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.195</v>
+        <v>-0.2218</v>
       </c>
       <c r="V6" t="n">
         <v>1.7614</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ALBISU ASTIGARRAGA</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7078</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.781</v>
+        <v>-2.2329</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4888</v>
+        <v>2.9328</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5952</v>
+        <v>0.0471</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0661</v>
+        <v>-0.3892</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5291</v>
+        <v>0.4363</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8087</v>
+        <v>0.4676</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8008</v>
+        <v>0.419</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0486</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2135</v>
+        <v>-0.4205</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7347</v>
+        <v>-0.8082</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5212</v>
+        <v>0.3877</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.0881</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8252</v>
+        <v>-2.8951</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2763</v>
+        <v>1.5933</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5063</v>
+        <v>0.1947</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7826</v>
+        <v>1.3986</v>
       </c>
       <c r="V7" t="n">
-        <v>1.9245</v>
+        <v>0.4106</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8173</v>
+        <v>0.4106</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RUIZ ALCALA</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2753</v>
+        <v>0.0077</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7252</v>
+        <v>-1.9788</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4499</v>
+        <v>1.9866</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3526</v>
+        <v>-0.759</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5268</v>
+        <v>0.946</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1742</v>
+        <v>-1.7051</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6062</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6469</v>
+        <v>1.3402</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>-2.0928</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2536</v>
+        <v>-0.0065</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1201</v>
+        <v>-0.3942</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>0.3877</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.386</v>
+        <v>2.8951</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3087</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.119</v>
+        <v>0.395</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1897</v>
+        <v>0.1206</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.6789</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0226</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>G. RUIZ ALCALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6248</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3169</v>
+        <v>-0.5656</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6921</v>
+        <v>0.4767</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.759</v>
+        <v>-0.3526</v>
       </c>
       <c r="H9" t="n">
-        <v>0.946</v>
+        <v>-0.5268</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7051</v>
+        <v>0.1742</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.6062</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3402</v>
+        <v>-0.6469</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0928</v>
+        <v>0.0407</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0065</v>
+        <v>0.2536</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3942</v>
+        <v>0.1201</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3877</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8951</v>
+        <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.117</v>
+        <v>-0.1223</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0569</v>
+        <v>0.0407</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1739</v>
+        <v>-0.1629</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6789</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8091</v>
+        <v>-0.8159999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5406</v>
+        <v>0.3998</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3497</v>
+        <v>-1.2159</v>
       </c>
       <c r="G10" t="n">
         <v>-1.0179</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2664</v>
+        <v>0.2594</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5777</v>
+        <v>0.4369</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3113</v>
+        <v>-0.1775</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0226</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2671</v>
+        <v>-2.282</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1353</v>
+        <v>-3.0163</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8682</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.6415999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7581</v>
+        <v>0.7433</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3437</v>
+        <v>-0.2247</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1018</v>
+        <v>0.968</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3508</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.1189</v>
+        <v>10.3087</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.286099999999999</v>
+        <v>-4.0964</v>
       </c>
       <c r="F12" t="n">
         <v>14.405</v>
@@ -1363,7 +1363,7 @@
         <v>-2.6705</v>
       </c>
       <c r="J12" t="n">
-        <v>6.473000000000002</v>
+        <v>6.473</v>
       </c>
       <c r="K12" t="n">
         <v>10.3178</v>
@@ -1390,10 +1390,10 @@
         <v>17.3707</v>
       </c>
       <c r="S12" t="n">
-        <v>5.4199</v>
+        <v>6.609899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2777999999999999</v>
+        <v>1.4677</v>
       </c>
       <c r="U12" t="n">
         <v>5.1422</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.3657</v>
+        <v>2.0375</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2538</v>
+        <v>2.2882</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1119</v>
+        <v>-0.2507</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7198</v>
+        <v>1.6798</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1067</v>
+        <v>-0.2152</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8265</v>
+        <v>1.895</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8598</v>
+        <v>3.3283</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6881</v>
+        <v>1.4075</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1717</v>
+        <v>1.9207</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.14</v>
+        <v>-1.6484</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7948</v>
+        <v>-1.6227</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6546999999999999</v>
+        <v>-0.0257</v>
       </c>
       <c r="P13" t="n">
+        <v>1.5441</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-1.158</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-3.0881</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.9301</v>
+        <v>2.7021</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7099</v>
+        <v>-0.8583</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0317</v>
+        <v>-1.0678</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6782</v>
+        <v>0.2095</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5138</v>
+        <v>-0.3281</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5138</v>
+        <v>1.1857</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2297</v>
+        <v>2.027</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7576</v>
+        <v>0.354</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5278</v>
+        <v>1.673</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3372</v>
+        <v>1.7198</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5589</v>
+        <v>-0.1067</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7783</v>
+        <v>1.8265</v>
       </c>
       <c r="J14" t="n">
-        <v>1.624</v>
+        <v>1.8598</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9729</v>
+        <v>0.6881</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6512</v>
+        <v>1.1717</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2869</v>
+        <v>-0.14</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.414</v>
+        <v>-0.7948</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1271</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R14" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2076</v>
+        <v>-0.0486</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1335</v>
+        <v>0.0684</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3411</v>
+        <v>-0.117</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2288</v>
+        <v>1.4634</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9877</v>
+        <v>1.8577</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7589</v>
+        <v>-0.3943</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6798</v>
+        <v>1.3372</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2152</v>
+        <v>0.5589</v>
       </c>
       <c r="I15" t="n">
-        <v>1.895</v>
+        <v>0.7783</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3283</v>
+        <v>1.624</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4075</v>
+        <v>0.9729</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9207</v>
+        <v>0.6512</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6484</v>
+        <v>-0.2869</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6227</v>
+        <v>-0.414</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0257</v>
+        <v>0.1271</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7021</v>
+        <v>0.386</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.667</v>
+        <v>0.0261</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3682</v>
+        <v>0.2337</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2988</v>
+        <v>-0.2076</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3281</v>
+        <v>-0.2859</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5138</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>S. LOPEZ RAMOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4063</v>
+        <v>0.4474</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1373</v>
+        <v>0.2544</v>
       </c>
       <c r="F16" t="n">
-        <v>0.269</v>
+        <v>0.193</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8317</v>
+        <v>0.1542</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9067</v>
+        <v>0.0207</v>
       </c>
       <c r="I16" t="n">
-        <v>0.075</v>
+        <v>0.1335</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5448</v>
+        <v>0.0207</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6262</v>
+        <v>0.0207</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2869</v>
+        <v>0.1335</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2805</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0064</v>
+        <v>0.1335</v>
       </c>
       <c r="P16" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.852</v>
+        <v>0.2931</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6821</v>
+        <v>0.2337</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1699</v>
+        <v>0.0595</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LOPEZ RAMOS</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3472</v>
+        <v>-0.0745</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1542</v>
+        <v>-0.2632</v>
       </c>
       <c r="F17" t="n">
-        <v>0.193</v>
+        <v>0.1887</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1542</v>
+        <v>-0.8317</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0207</v>
+        <v>-0.9067</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1335</v>
+        <v>0.075</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0207</v>
+        <v>-0.5448</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0207</v>
+        <v>-0.6262</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0814</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1335</v>
+        <v>-0.2869</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.2805</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1335</v>
+        <v>-0.0064</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="S17" t="n">
-        <v>0.193</v>
+        <v>0.3711</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1335</v>
+        <v>0.2816</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0595</v>
+        <v>0.0896</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2474</v>
+        <v>-0.3277</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1164</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.131</v>
+        <v>-0.2113</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4318</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2016</v>
+        <v>-0.2819</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0231</v>
+        <v>-0.1035</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0978</v>
+        <v>-1.0713</v>
       </c>
       <c r="E19" t="n">
         <v>-1.1051</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0073</v>
+        <v>0.0338</v>
       </c>
       <c r="G19" t="n">
         <v>1.9448</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4865</v>
+        <v>-0.46</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5949</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1084</v>
+        <v>0.1348</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1701</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7669</v>
+        <v>-1.4483</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.6206</v>
+        <v>-1.7886</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8538</v>
+        <v>0.3403</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3143</v>
+        <v>0.6963</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1262</v>
+        <v>-1.2151</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.4405</v>
+        <v>1.9114</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5136</v>
+        <v>1.704</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7023</v>
+        <v>0.4345</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.2159</v>
+        <v>1.2695</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8007</v>
+        <v>-1.0077</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5761</v>
+        <v>-1.6496</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7754</v>
+        <v>0.6419</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3511</v>
+        <v>-2.3161</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0881</v>
+        <v>3.2811</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5334</v>
+        <v>-0.9396</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0575</v>
+        <v>-1.4624</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5241</v>
+        <v>0.5228</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6562</v>
+        <v>-2.1701</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6985</v>
+        <v>0.2859</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0422</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9271</v>
+        <v>-1.7678</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4134</v>
+        <v>-4.6206</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4863</v>
+        <v>2.8528</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3508</v>
+        <v>-2.3143</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9717</v>
+        <v>0.1262</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3792</v>
+        <v>-2.4405</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1496</v>
+        <v>-1.5136</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1903</v>
+        <v>1.7023</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0407</v>
+        <v>-3.2159</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2012</v>
+        <v>-0.8007</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7813</v>
+        <v>-1.5761</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4199</v>
+        <v>0.7754</v>
       </c>
       <c r="P21" t="n">
-        <v>0.386</v>
+        <v>1.7371</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.158</v>
+        <v>-1.3511</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>3.0881</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0377</v>
+        <v>-0.5344</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1057</v>
+        <v>-1.0575</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1434</v>
+        <v>0.5231</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6985</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9396</v>
+        <v>-2.0533</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6479</v>
+        <v>-3.9484</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7083</v>
+        <v>1.895</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1188</v>
@@ -2170,13 +2170,13 @@
         <v>2.3161</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.7463</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8791</v>
+        <v>-1.1795</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2465</v>
+        <v>0.4332</v>
       </c>
       <c r="V22" t="n">
         <v>2.7418</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2696</v>
+        <v>-2.1472</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2893</v>
+        <v>-2.7138</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0197</v>
+        <v>0.5666</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6963</v>
+        <v>-2.3508</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2151</v>
+        <v>-1.9717</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9114</v>
+        <v>-0.3792</v>
       </c>
       <c r="J23" t="n">
-        <v>1.704</v>
+        <v>-1.1496</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4345</v>
+        <v>-1.1903</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2695</v>
+        <v>0.0407</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0077</v>
+        <v>-1.2012</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6496</v>
+        <v>-0.7813</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6419</v>
+        <v>-0.4199</v>
       </c>
       <c r="P23" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3161</v>
+        <v>-1.158</v>
       </c>
       <c r="R23" t="n">
-        <v>3.2811</v>
+        <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7609</v>
+        <v>-0.1824</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9631</v>
+        <v>-0.4062</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2022</v>
+        <v>0.2237</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1701</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4485</v>
+        <v>-4.2013</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.503</v>
+        <v>-4.6031</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0545</v>
+        <v>0.4019</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2223</v>
@@ -2326,13 +2326,13 @@
         <v>1.5441</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3034</v>
+        <v>-0.0562</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0873</v>
+        <v>-0.0129</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3907</v>
+        <v>-0.0433</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5717</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.119199999999999</v>
+        <v>-7.116099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.4051</v>
+        <v>-14.4049</v>
       </c>
       <c r="F25" t="n">
-        <v>5.2861</v>
+        <v>7.2888</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7376</v>
@@ -2377,10 +2377,10 @@
         <v>2.6703</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7353</v>
+        <v>3.735300000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9098</v>
+        <v>4.909800000000001</v>
       </c>
       <c r="L25" t="n">
         <v>-1.1745</v>
@@ -2395,7 +2395,7 @@
         <v>3.8448</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9650000000000005</v>
+        <v>0.9650000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>-17.3706</v>
@@ -2404,13 +2404,13 @@
         <v>18.3357</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.420199999999999</v>
+        <v>-3.4174</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.1423</v>
+        <v>-5.142300000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2779000000000001</v>
+        <v>1.7248</v>
       </c>
       <c r="V25" t="n">
         <v>-1.9265</v>
@@ -2419,7 +2419,7 @@
         <v>4.3725</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.2989</v>
+        <v>-6.298900000000001</v>
       </c>
     </row>
   </sheetData>
